--- a/output/pdf_financials_xlsx/BOOM.xlsx
+++ b/output/pdf_financials_xlsx/BOOM.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.968746</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.042869</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.01059</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.1475</v>
+        <v>2.116246</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.060369</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.01059</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.971746</v>
+        <v>0.003</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.053484</v>
+        <v>0.010615</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.102584</v>
+        <v>0.09199400000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/BOOM.xlsx
+++ b/output/pdf_financials_xlsx/BOOM.xlsx
@@ -2308,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.083588</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.010525</v>
       </c>
     </row>
     <row r="116">
@@ -3659,7 +3659,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -4649,7 +4653,11 @@
           <t>Interest revenues</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
